--- a/ejercicios.xlsx
+++ b/ejercicios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jamas\Documents\01 app W360 jO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86197BE-0143-46B0-9503-71A2167DCEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD1E445-ACFE-4820-B723-45F5D0D41991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="303">
   <si>
     <t>ID_Rutina</t>
   </si>
@@ -497,9 +497,6 @@
     <t>Triceps con mancuerna bilateral en suelo</t>
   </si>
   <si>
-    <t>Triceps</t>
-  </si>
-  <si>
     <t>Triceps con mancuerna unilateral en suelo</t>
   </si>
   <si>
@@ -636,6 +633,309 @@
   </si>
   <si>
     <t>https://i.ibb.co/4RsBXqCG/EJ031.png</t>
+  </si>
+  <si>
+    <t>Deltoides anterior, sentado, agarre neutro</t>
+  </si>
+  <si>
+    <t>Deltoides anterior, sentado, agarre prono</t>
+  </si>
+  <si>
+    <t>Deltoides anterior, de pie, agarre neutro</t>
+  </si>
+  <si>
+    <t>Deltoides anterior, de pie, agarre prono</t>
+  </si>
+  <si>
+    <t>Deltoides anterior, de pie, agarre supino</t>
+  </si>
+  <si>
+    <t>Deltoides lateral, tumbado, agarre neutro</t>
+  </si>
+  <si>
+    <t>Deltoides lateral, sentado, abduccion agarre prono</t>
+  </si>
+  <si>
+    <t>Combo: Deltoides y rotadores externos</t>
+  </si>
+  <si>
+    <t>Deltoides lateral, de pie, abduccion agarre prono, gomas</t>
+  </si>
+  <si>
+    <t>Deltoides lateral, de pie, abduccion agarre prono, pesas</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/1tqnby5G/EJ032.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/ymcpWnXb/EJ033-1.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/6cn6PZbg/EJ033.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/CKYdnJJg/EJ034.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/vxCpKkLB/EJ035.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/pvnwfxxG/EJ036.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/LDn16dYQ/EJ037-1.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/GfHxMBq5/EJ037-2.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/h1m65VPX/EJ037-3.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/yFf1XqT7/EJ038.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/RG1bggts/EJ039-1.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/twkgn817/EJ039-2.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/SH0gpKs/EJ040-1.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/B5xN5JyL/EJ040-2.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/wrRkcnPq/EJ041.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/fV9fh3cd/EJ042.png</t>
+  </si>
+  <si>
+    <t>EJ060</t>
+  </si>
+  <si>
+    <t>EJ061</t>
+  </si>
+  <si>
+    <t>EJ062</t>
+  </si>
+  <si>
+    <t>EJ063</t>
+  </si>
+  <si>
+    <t>EJ064</t>
+  </si>
+  <si>
+    <t>EJ065</t>
+  </si>
+  <si>
+    <t>EJ066</t>
+  </si>
+  <si>
+    <t>EJ067</t>
+  </si>
+  <si>
+    <t>EJ068</t>
+  </si>
+  <si>
+    <t>EJ069</t>
+  </si>
+  <si>
+    <t>EJ070</t>
+  </si>
+  <si>
+    <t>EJ071</t>
+  </si>
+  <si>
+    <t>EJ072</t>
+  </si>
+  <si>
+    <t>EJ073</t>
+  </si>
+  <si>
+    <t>EJ074</t>
+  </si>
+  <si>
+    <t>EJ075</t>
+  </si>
+  <si>
+    <t>EJ076</t>
+  </si>
+  <si>
+    <t>EJ077</t>
+  </si>
+  <si>
+    <t>EJ078</t>
+  </si>
+  <si>
+    <t>EJ079</t>
+  </si>
+  <si>
+    <t>EJ080</t>
+  </si>
+  <si>
+    <t>EJ081</t>
+  </si>
+  <si>
+    <t>EJ082</t>
+  </si>
+  <si>
+    <t>EJ083</t>
+  </si>
+  <si>
+    <t>EJ084</t>
+  </si>
+  <si>
+    <t>EJ085</t>
+  </si>
+  <si>
+    <t>EJ086</t>
+  </si>
+  <si>
+    <t>EJ087</t>
+  </si>
+  <si>
+    <t>EJ088</t>
+  </si>
+  <si>
+    <t>EJ089</t>
+  </si>
+  <si>
+    <t>EJ090</t>
+  </si>
+  <si>
+    <t>EJ091</t>
+  </si>
+  <si>
+    <t>EJ092</t>
+  </si>
+  <si>
+    <t>EJ093</t>
+  </si>
+  <si>
+    <t>EJ094</t>
+  </si>
+  <si>
+    <t>EJ095</t>
+  </si>
+  <si>
+    <t>EJ096</t>
+  </si>
+  <si>
+    <t>EJ097</t>
+  </si>
+  <si>
+    <t>EJ098</t>
+  </si>
+  <si>
+    <t>EJ099</t>
+  </si>
+  <si>
+    <t>EJ100</t>
+  </si>
+  <si>
+    <t>EJ101</t>
+  </si>
+  <si>
+    <t>EJ102</t>
+  </si>
+  <si>
+    <t>Biceps, agarre neutro, alternativo</t>
+  </si>
+  <si>
+    <t>Brazos</t>
+  </si>
+  <si>
+    <t>Biceps, agarre neutro, bilateral</t>
+  </si>
+  <si>
+    <t>Postural</t>
+  </si>
+  <si>
+    <t>Serrato anterior, de pie, antebrazos, deslizamiento bilateral</t>
+  </si>
+  <si>
+    <t>Serrato anterior, de pie, push up plus (deslizamiento bilateral)</t>
+  </si>
+  <si>
+    <t>Serrato anterior, cuadrupedia, deslizamiento bilateral</t>
+  </si>
+  <si>
+    <t>Serrato anterior, superman, deslizamiento unilateral</t>
+  </si>
+  <si>
+    <t>Serrato anterior, supino sobre churro, deslizamiento bilateral</t>
+  </si>
+  <si>
+    <t>Serrato anterior, prono en el suelo, deslizamiento bilateral</t>
+  </si>
+  <si>
+    <t>Serrato anterior, prono sobre banco, deslizamiento bilateral</t>
+  </si>
+  <si>
+    <t>Serrato anterior, lateral, press escapula</t>
+  </si>
+  <si>
+    <t>Serrato anterior, de pie, flexion rodada con gomas</t>
+  </si>
+  <si>
+    <t>Serrato anterior, de rodillas, flexion rodada con gomas</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/V0xtBB35/EJ043.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/RTBJbbJq/EJ044.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/hRQ7QpPm/EJ045-2.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/TycdMcV/EJ045-1.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/CsbrLgdq/EJ046.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/b5TSGm3d/EJ047-2.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/Tx6bWjyd/EJ047-1.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/pBYhYCDC/EJ048.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/FL72tpVn/EJ049-2.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/436Cy4P/EJ049-1.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/DPTG9VCB/EJ050.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/Fr6CB7p/EJ051-2.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/C33cPXD1/EJ051-1.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/b5jcbzNc/EJ052-2.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/B2XSD2YT/EJ052-1.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/20HcCY5S/EJ053-2.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/DgwzT61Y/EJ053-1.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/KjX6T2zY/EJ054.png</t>
   </si>
 </sst>
 </file>
@@ -645,7 +945,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -700,6 +1000,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -805,7 +1111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -865,6 +1171,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1093,10 +1402,11 @@
   <dimension ref="A1:S1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="30.5703125" customWidth="1"/>
+    <col min="2" max="2" width="53.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="16.28515625" customWidth="1"/>
-    <col min="8" max="11" width="16.7109375" customWidth="1"/>
+    <col min="8" max="9" width="16.7109375" style="25" customWidth="1"/>
+    <col min="10" max="11" width="16.7109375" customWidth="1"/>
     <col min="13" max="13" width="30.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1108,7 +1418,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
@@ -1122,10 +1432,10 @@
       <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="10" t="s">
         <v>17</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -1146,13 +1456,13 @@
         <v>25</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>27</v>
@@ -1182,13 +1492,13 @@
         <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>27</v>
@@ -1214,13 +1524,13 @@
         <v>51</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>24</v>
@@ -1246,13 +1556,13 @@
         <v>55</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>24</v>
@@ -1276,13 +1586,13 @@
         <v>58</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>27</v>
@@ -1308,13 +1618,13 @@
         <v>63</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>27</v>
@@ -1340,13 +1650,13 @@
         <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>24</v>
@@ -1370,13 +1680,13 @@
         <v>71</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>24</v>
@@ -1402,13 +1712,13 @@
         <v>75</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>27</v>
@@ -1436,13 +1746,13 @@
         <v>81</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>27</v>
@@ -1468,13 +1778,13 @@
         <v>85</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>24</v>
@@ -1498,13 +1808,13 @@
         <v>88</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>24</v>
@@ -1534,13 +1844,13 @@
         <v>94</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>27</v>
@@ -1564,13 +1874,13 @@
         <v>97</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>24</v>
@@ -1598,13 +1908,13 @@
         <v>102</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>24</v>
@@ -1628,13 +1938,13 @@
         <v>105</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>27</v>
@@ -1658,13 +1968,13 @@
         <v>108</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>24</v>
@@ -1696,13 +2006,13 @@
         <v>111</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>24</v>
@@ -1732,13 +2042,13 @@
         <v>155</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>156</v>
+        <v>177</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>272</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>27</v>
@@ -1747,13 +2057,13 @@
         <v>59</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L20" s="13"/>
       <c r="N20" s="14"/>
@@ -1768,29 +2078,29 @@
         <v>114</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>156</v>
+        <v>177</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>272</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>27</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="I21" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="I21" s="22" t="s">
+      <c r="J21" s="22" t="s">
         <v>169</v>
-      </c>
-      <c r="J21" s="22" t="s">
-        <v>170</v>
       </c>
       <c r="L21" s="13"/>
       <c r="N21" s="14"/>
@@ -1805,16 +2115,16 @@
         <v>115</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>156</v>
+        <v>177</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>272</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F22" s="20" t="s">
         <v>27</v>
@@ -1823,10 +2133,10 @@
         <v>59</v>
       </c>
       <c r="H22" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="I22" s="22" t="s">
         <v>166</v>
-      </c>
-      <c r="I22" s="22" t="s">
-        <v>167</v>
       </c>
       <c r="L22" s="13"/>
       <c r="N22" s="14"/>
@@ -1841,16 +2151,16 @@
         <v>116</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>156</v>
+        <v>177</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>272</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>24</v>
@@ -1859,13 +2169,13 @@
         <v>59</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I23" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L23" s="13"/>
       <c r="N23" s="14"/>
@@ -1880,16 +2190,16 @@
         <v>117</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>156</v>
+        <v>177</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>272</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>24</v>
@@ -1898,13 +2208,13 @@
         <v>59</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L24" s="13"/>
       <c r="N24" s="14"/>
@@ -1919,16 +2229,16 @@
         <v>118</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>156</v>
+        <v>177</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>272</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>27</v>
@@ -1937,7 +2247,7 @@
         <v>47</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
@@ -1953,16 +2263,16 @@
         <v>119</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>156</v>
+        <v>177</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>272</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>27</v>
@@ -1971,7 +2281,7 @@
         <v>59</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
@@ -1987,16 +2297,16 @@
         <v>120</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>156</v>
+        <v>177</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>272</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>24</v>
@@ -2005,7 +2315,7 @@
         <v>59</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
@@ -2021,16 +2331,16 @@
         <v>121</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D28" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E28" s="23" t="s">
         <v>184</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>185</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>27</v>
@@ -2039,10 +2349,10 @@
         <v>59</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I28" s="22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J28" s="10"/>
       <c r="N28" s="14"/>
@@ -2057,16 +2367,16 @@
         <v>122</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D29" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E29" s="23" t="s">
         <v>184</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>185</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>27</v>
@@ -2075,7 +2385,7 @@
         <v>59</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J29" s="10"/>
       <c r="M29" s="14"/>
@@ -2091,16 +2401,16 @@
         <v>123</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D30" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" s="23" t="s">
         <v>184</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>185</v>
       </c>
       <c r="F30" s="20" t="s">
         <v>24</v>
@@ -2109,13 +2419,13 @@
         <v>59</v>
       </c>
       <c r="H30" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="I30" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="I30" s="22" t="s">
+      <c r="J30" s="22" t="s">
         <v>197</v>
-      </c>
-      <c r="J30" s="22" t="s">
-        <v>198</v>
       </c>
       <c r="M30" s="14"/>
       <c r="N30" s="14"/>
@@ -2130,16 +2440,16 @@
         <v>124</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D31" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" s="23" t="s">
         <v>184</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>185</v>
       </c>
       <c r="F31" s="20" t="s">
         <v>27</v>
@@ -2148,10 +2458,10 @@
         <v>59</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
@@ -2166,16 +2476,16 @@
         <v>125</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D32" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E32" s="23" t="s">
         <v>184</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>185</v>
       </c>
       <c r="F32" s="20" t="s">
         <v>27</v>
@@ -2184,10 +2494,10 @@
         <v>47</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J32" s="10"/>
       <c r="M32" s="14"/>
@@ -2202,8 +2512,28 @@
       <c r="A33" s="4" t="s">
         <v>126</v>
       </c>
+      <c r="B33" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>212</v>
+      </c>
       <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
       <c r="O33" s="14"/>
@@ -2216,9 +2546,30 @@
       <c r="A34" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
+      <c r="B34" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="I34" s="24" t="s">
+        <v>213</v>
+      </c>
       <c r="K34" s="13"/>
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
@@ -2232,9 +2583,28 @@
       <c r="A35" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H35" s="10"/>
+      <c r="B35" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H35" s="24" t="s">
+        <v>215</v>
+      </c>
       <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
       <c r="K35" s="13"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
@@ -2248,9 +2618,28 @@
       <c r="A36" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H36" s="10"/>
+      <c r="B36" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H36" s="24" t="s">
+        <v>216</v>
+      </c>
       <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
       <c r="K36" s="13"/>
       <c r="L36" s="13"/>
       <c r="M36" s="14"/>
@@ -2265,9 +2654,28 @@
       <c r="A37" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="H37" s="10"/>
+      <c r="B37" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H37" s="24" t="s">
+        <v>217</v>
+      </c>
       <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
       <c r="K37" s="13"/>
       <c r="L37" s="13"/>
       <c r="M37" s="14"/>
@@ -2282,9 +2690,33 @@
       <c r="A38" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
+      <c r="B38" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="I38" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J38" s="24" t="s">
+        <v>220</v>
+      </c>
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
     </row>
@@ -2292,9 +2724,28 @@
       <c r="A39" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H39" s="10"/>
+      <c r="B39" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H39" s="24" t="s">
+        <v>221</v>
+      </c>
       <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
     </row>
@@ -2302,9 +2753,30 @@
       <c r="A40" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
+      <c r="B40" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H40" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="I40" s="24" t="s">
+        <v>223</v>
+      </c>
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
     </row>
@@ -2312,9 +2784,30 @@
       <c r="A41" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
+      <c r="B41" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D41" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H41" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="I41" s="24" t="s">
+        <v>225</v>
+      </c>
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
     </row>
@@ -2322,49 +2815,142 @@
       <c r="A42" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="H42" s="10"/>
+      <c r="B42" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D42" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H42" s="24" t="s">
+        <v>226</v>
+      </c>
       <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
       <c r="L42" s="10"/>
     </row>
     <row r="43" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="H43" s="10"/>
+      <c r="B43" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E43" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H43" s="24" t="s">
+        <v>227</v>
+      </c>
       <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
       <c r="L43" s="10"/>
     </row>
     <row r="44" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="H44" s="10"/>
+      <c r="B44" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="E44" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H44" s="24" t="s">
+        <v>285</v>
+      </c>
       <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
       <c r="L44" s="10"/>
     </row>
     <row r="45" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="H45" s="10"/>
+      <c r="B45" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H45" s="24" t="s">
+        <v>286</v>
+      </c>
       <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
       <c r="L45" s="10"/>
     </row>
     <row r="46" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
+      <c r="B46" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H46" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="I46" s="24" t="s">
+        <v>287</v>
+      </c>
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
     </row>
@@ -2372,9 +2958,28 @@
       <c r="A47" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H47" s="10"/>
+      <c r="B47" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G47" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H47" s="24" t="s">
+        <v>289</v>
+      </c>
       <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
     </row>
@@ -2382,9 +2987,30 @@
       <c r="A48" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
+      <c r="B48" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="I48" s="24" t="s">
+        <v>290</v>
+      </c>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
     </row>
@@ -2392,9 +3018,27 @@
       <c r="A49" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
+      <c r="B49" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E49" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" s="24" t="s">
+        <v>292</v>
+      </c>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
     </row>
@@ -2402,9 +3046,30 @@
       <c r="A50" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
+      <c r="B50" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H50" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="I50" s="24" t="s">
+        <v>294</v>
+      </c>
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
     </row>
@@ -2412,9 +3077,28 @@
       <c r="A51" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="H51" s="10"/>
+      <c r="B51" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F51" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>295</v>
+      </c>
       <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
       <c r="K51" s="10"/>
       <c r="L51" s="10"/>
     </row>
@@ -2422,9 +3106,30 @@
       <c r="A52" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
+      <c r="B52" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F52" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H52" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="I52" s="24" t="s">
+        <v>296</v>
+      </c>
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
     </row>
@@ -2432,9 +3137,30 @@
       <c r="A53" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
+      <c r="B53" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H53" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="I53" s="24" t="s">
+        <v>298</v>
+      </c>
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
     </row>
@@ -2442,9 +3168,30 @@
       <c r="A54" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
+      <c r="B54" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E54" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H54" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="I54" s="24" t="s">
+        <v>300</v>
+      </c>
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
     </row>
@@ -2452,9 +3199,28 @@
       <c r="A55" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="H55" s="10"/>
+      <c r="B55" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D55" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E55" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H55" s="24" t="s">
+        <v>302</v>
+      </c>
       <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
       <c r="K55" s="10"/>
       <c r="L55" s="10"/>
     </row>
@@ -2464,7 +3230,6 @@
       </c>
       <c r="H56" s="10"/>
       <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
     </row>
@@ -2474,7 +3239,6 @@
       </c>
       <c r="H57" s="10"/>
       <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
       <c r="K57" s="10"/>
       <c r="L57" s="10"/>
     </row>
@@ -2484,7 +3248,6 @@
       </c>
       <c r="H58" s="10"/>
       <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
     </row>
@@ -2494,7 +3257,6 @@
       </c>
       <c r="H59" s="10"/>
       <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
       <c r="K59" s="10"/>
       <c r="L59" s="10"/>
     </row>
@@ -2509,6 +3271,9 @@
       <c r="L60" s="10"/>
     </row>
     <row r="61" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>228</v>
+      </c>
       <c r="H61" s="10"/>
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
@@ -2516,6 +3281,9 @@
       <c r="L61" s="10"/>
     </row>
     <row r="62" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>229</v>
+      </c>
       <c r="H62" s="10"/>
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
@@ -2523,6 +3291,9 @@
       <c r="L62" s="10"/>
     </row>
     <row r="63" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>230</v>
+      </c>
       <c r="H63" s="10"/>
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
@@ -2530,342 +3301,462 @@
       <c r="L63" s="10"/>
     </row>
     <row r="64" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>231</v>
+      </c>
       <c r="H64" s="10"/>
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
       <c r="L64" s="10"/>
     </row>
-    <row r="65" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>232</v>
+      </c>
       <c r="H65" s="10"/>
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
       <c r="L65" s="10"/>
     </row>
-    <row r="66" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>233</v>
+      </c>
       <c r="H66" s="10"/>
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
       <c r="L66" s="10"/>
     </row>
-    <row r="67" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>234</v>
+      </c>
       <c r="H67" s="10"/>
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
       <c r="L67" s="10"/>
     </row>
-    <row r="68" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>235</v>
+      </c>
       <c r="H68" s="10"/>
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
       <c r="L68" s="10"/>
     </row>
-    <row r="69" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>236</v>
+      </c>
       <c r="H69" s="10"/>
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
     </row>
-    <row r="70" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>237</v>
+      </c>
       <c r="H70" s="10"/>
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
       <c r="L70" s="10"/>
     </row>
-    <row r="71" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
+        <v>238</v>
+      </c>
       <c r="H71" s="10"/>
       <c r="I71" s="10"/>
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
       <c r="L71" s="10"/>
     </row>
-    <row r="72" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
+        <v>239</v>
+      </c>
       <c r="H72" s="10"/>
       <c r="I72" s="10"/>
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
       <c r="L72" s="10"/>
     </row>
-    <row r="73" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
+        <v>240</v>
+      </c>
       <c r="H73" s="10"/>
       <c r="I73" s="10"/>
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
       <c r="L73" s="10"/>
     </row>
-    <row r="74" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="4" t="s">
+        <v>241</v>
+      </c>
       <c r="H74" s="10"/>
       <c r="I74" s="10"/>
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
       <c r="L74" s="10"/>
     </row>
-    <row r="75" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
+        <v>242</v>
+      </c>
       <c r="H75" s="10"/>
       <c r="I75" s="10"/>
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
       <c r="L75" s="10"/>
     </row>
-    <row r="76" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>243</v>
+      </c>
       <c r="H76" s="10"/>
       <c r="I76" s="10"/>
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
       <c r="L76" s="10"/>
     </row>
-    <row r="77" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>244</v>
+      </c>
       <c r="H77" s="10"/>
       <c r="I77" s="10"/>
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
       <c r="L77" s="10"/>
     </row>
-    <row r="78" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>245</v>
+      </c>
       <c r="H78" s="10"/>
       <c r="I78" s="10"/>
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
       <c r="L78" s="10"/>
     </row>
-    <row r="79" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
+        <v>246</v>
+      </c>
       <c r="H79" s="10"/>
       <c r="I79" s="10"/>
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
       <c r="L79" s="10"/>
     </row>
-    <row r="80" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
+        <v>247</v>
+      </c>
       <c r="H80" s="10"/>
       <c r="I80" s="10"/>
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
       <c r="L80" s="10"/>
     </row>
-    <row r="81" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
+        <v>248</v>
+      </c>
       <c r="H81" s="10"/>
       <c r="I81" s="10"/>
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
       <c r="L81" s="10"/>
     </row>
-    <row r="82" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="4" t="s">
+        <v>249</v>
+      </c>
       <c r="H82" s="10"/>
       <c r="I82" s="10"/>
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
       <c r="L82" s="10"/>
     </row>
-    <row r="83" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
+        <v>250</v>
+      </c>
       <c r="H83" s="10"/>
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
       <c r="L83" s="10"/>
     </row>
-    <row r="84" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="4" t="s">
+        <v>251</v>
+      </c>
       <c r="H84" s="10"/>
       <c r="I84" s="10"/>
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
       <c r="L84" s="10"/>
     </row>
-    <row r="85" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="4" t="s">
+        <v>252</v>
+      </c>
       <c r="H85" s="10"/>
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
       <c r="K85" s="10"/>
       <c r="L85" s="10"/>
     </row>
-    <row r="86" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="4" t="s">
+        <v>253</v>
+      </c>
       <c r="H86" s="10"/>
       <c r="I86" s="10"/>
       <c r="J86" s="10"/>
       <c r="K86" s="10"/>
       <c r="L86" s="10"/>
     </row>
-    <row r="87" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="4" t="s">
+        <v>254</v>
+      </c>
       <c r="H87" s="10"/>
       <c r="I87" s="10"/>
       <c r="J87" s="10"/>
       <c r="K87" s="10"/>
       <c r="L87" s="10"/>
     </row>
-    <row r="88" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="4" t="s">
+        <v>255</v>
+      </c>
       <c r="H88" s="10"/>
       <c r="I88" s="10"/>
       <c r="J88" s="10"/>
       <c r="K88" s="10"/>
       <c r="L88" s="10"/>
     </row>
-    <row r="89" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="4" t="s">
+        <v>256</v>
+      </c>
       <c r="H89" s="10"/>
       <c r="I89" s="10"/>
       <c r="J89" s="10"/>
       <c r="K89" s="10"/>
       <c r="L89" s="10"/>
     </row>
-    <row r="90" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
+        <v>257</v>
+      </c>
       <c r="H90" s="10"/>
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
       <c r="K90" s="10"/>
       <c r="L90" s="10"/>
     </row>
-    <row r="91" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="4" t="s">
+        <v>258</v>
+      </c>
       <c r="H91" s="10"/>
       <c r="I91" s="10"/>
       <c r="J91" s="10"/>
       <c r="K91" s="10"/>
       <c r="L91" s="10"/>
     </row>
-    <row r="92" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="4" t="s">
+        <v>259</v>
+      </c>
       <c r="H92" s="10"/>
       <c r="I92" s="10"/>
       <c r="J92" s="10"/>
       <c r="K92" s="10"/>
       <c r="L92" s="10"/>
     </row>
-    <row r="93" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
+        <v>260</v>
+      </c>
       <c r="H93" s="10"/>
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
       <c r="K93" s="10"/>
       <c r="L93" s="10"/>
     </row>
-    <row r="94" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="4" t="s">
+        <v>261</v>
+      </c>
       <c r="H94" s="10"/>
       <c r="I94" s="10"/>
       <c r="J94" s="10"/>
       <c r="K94" s="10"/>
       <c r="L94" s="10"/>
     </row>
-    <row r="95" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="4" t="s">
+        <v>262</v>
+      </c>
       <c r="H95" s="10"/>
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
       <c r="K95" s="10"/>
       <c r="L95" s="10"/>
     </row>
-    <row r="96" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="4" t="s">
+        <v>263</v>
+      </c>
       <c r="H96" s="10"/>
       <c r="I96" s="10"/>
       <c r="J96" s="10"/>
       <c r="K96" s="10"/>
       <c r="L96" s="10"/>
     </row>
-    <row r="97" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="4" t="s">
+        <v>264</v>
+      </c>
       <c r="H97" s="10"/>
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
       <c r="K97" s="10"/>
       <c r="L97" s="10"/>
     </row>
-    <row r="98" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="4" t="s">
+        <v>265</v>
+      </c>
       <c r="H98" s="10"/>
       <c r="I98" s="10"/>
       <c r="J98" s="10"/>
       <c r="K98" s="10"/>
       <c r="L98" s="10"/>
     </row>
-    <row r="99" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="4" t="s">
+        <v>266</v>
+      </c>
       <c r="H99" s="10"/>
       <c r="I99" s="10"/>
       <c r="J99" s="10"/>
       <c r="K99" s="10"/>
       <c r="L99" s="10"/>
     </row>
-    <row r="100" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="4" t="s">
+        <v>267</v>
+      </c>
       <c r="H100" s="10"/>
       <c r="I100" s="10"/>
       <c r="J100" s="10"/>
       <c r="K100" s="10"/>
       <c r="L100" s="10"/>
     </row>
-    <row r="101" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="4" t="s">
+        <v>268</v>
+      </c>
       <c r="H101" s="10"/>
       <c r="I101" s="10"/>
       <c r="J101" s="10"/>
       <c r="K101" s="10"/>
       <c r="L101" s="10"/>
     </row>
-    <row r="102" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="H102" s="10"/>
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
       <c r="K102" s="10"/>
       <c r="L102" s="10"/>
     </row>
-    <row r="103" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="4" t="s">
+        <v>270</v>
+      </c>
       <c r="H103" s="10"/>
       <c r="I103" s="10"/>
       <c r="J103" s="10"/>
       <c r="K103" s="10"/>
       <c r="L103" s="10"/>
     </row>
-    <row r="104" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H104" s="10"/>
       <c r="I104" s="10"/>
       <c r="J104" s="10"/>
       <c r="K104" s="10"/>
       <c r="L104" s="10"/>
     </row>
-    <row r="105" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H105" s="10"/>
       <c r="I105" s="10"/>
       <c r="J105" s="10"/>
       <c r="K105" s="10"/>
       <c r="L105" s="10"/>
     </row>
-    <row r="106" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H106" s="10"/>
       <c r="I106" s="10"/>
       <c r="J106" s="10"/>
       <c r="K106" s="10"/>
       <c r="L106" s="10"/>
     </row>
-    <row r="107" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H107" s="10"/>
       <c r="I107" s="10"/>
       <c r="J107" s="10"/>
       <c r="K107" s="10"/>
       <c r="L107" s="10"/>
     </row>
-    <row r="108" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H108" s="10"/>
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
       <c r="K108" s="10"/>
       <c r="L108" s="10"/>
     </row>
-    <row r="109" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H109" s="10"/>
       <c r="I109" s="10"/>
       <c r="J109" s="10"/>
       <c r="K109" s="10"/>
       <c r="L109" s="10"/>
     </row>
-    <row r="110" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H110" s="10"/>
       <c r="I110" s="10"/>
       <c r="J110" s="10"/>
       <c r="K110" s="10"/>
       <c r="L110" s="10"/>
     </row>
-    <row r="111" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H111" s="10"/>
       <c r="I111" s="10"/>
       <c r="J111" s="10"/>
       <c r="K111" s="10"/>
       <c r="L111" s="10"/>
     </row>
-    <row r="112" spans="8:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H112" s="10"/>
       <c r="I112" s="10"/>
       <c r="J112" s="10"/>
@@ -9089,6 +9980,7 @@
       <c r="L1000" s="10"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="I2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -9152,6 +10044,40 @@
     <hyperlink ref="J30" r:id="rId60" xr:uid="{249A51D3-0DC0-4896-8AA5-02B36A5DF8CA}"/>
     <hyperlink ref="H32" r:id="rId61" xr:uid="{C58AA6B0-C5D5-40CB-9DBF-7F740EC6A538}"/>
     <hyperlink ref="I32" r:id="rId62" xr:uid="{73BF5EFC-7B3F-45AD-AB23-8066898D5BFD}"/>
+    <hyperlink ref="H33" r:id="rId63" xr:uid="{3D9D6E99-3A25-4AE1-B03B-252F6ED6BECC}"/>
+    <hyperlink ref="H34" r:id="rId64" xr:uid="{DBCB1F7F-457B-475E-BF9C-CC1930F22C6E}"/>
+    <hyperlink ref="H35" r:id="rId65" xr:uid="{1EEB0C95-7F28-4D5D-BD39-9FE406F210ED}"/>
+    <hyperlink ref="H36" r:id="rId66" xr:uid="{C4E5F053-CCC9-491E-9E7B-3468283B2242}"/>
+    <hyperlink ref="H38" r:id="rId67" xr:uid="{1F523DEB-60FD-41DB-9840-8CF411E9DA60}"/>
+    <hyperlink ref="H37" r:id="rId68" xr:uid="{B540B5F6-EE95-440D-AC8A-76338929B9D7}"/>
+    <hyperlink ref="H39" r:id="rId69" xr:uid="{81FA1B1C-3E5A-4965-BC01-020058101338}"/>
+    <hyperlink ref="H40" r:id="rId70" xr:uid="{8EF03E53-DD11-4E0A-90F3-F63510BDC440}"/>
+    <hyperlink ref="H41" r:id="rId71" xr:uid="{DEE6239A-8F58-41F1-A916-58142D806A89}"/>
+    <hyperlink ref="H42" r:id="rId72" xr:uid="{BC687991-DC29-48D4-83B2-10269A769F33}"/>
+    <hyperlink ref="H43" r:id="rId73" xr:uid="{C474AFB6-A42A-4D09-84FF-C2D60EB73E6C}"/>
+    <hyperlink ref="I34" r:id="rId74" xr:uid="{869F29FA-4A0E-438D-A621-71E08D24DFA9}"/>
+    <hyperlink ref="I38" r:id="rId75" xr:uid="{A96B2351-290E-48AD-AB48-065858B9D744}"/>
+    <hyperlink ref="I40" r:id="rId76" xr:uid="{7F06344C-88BB-4C88-AB04-37B2FDF3D229}"/>
+    <hyperlink ref="I41" r:id="rId77" xr:uid="{C3178BC2-2399-4A3A-A53F-C0285A2C0495}"/>
+    <hyperlink ref="J38" r:id="rId78" xr:uid="{F696AD21-E865-4DE7-80D3-AD049013CED4}"/>
+    <hyperlink ref="H44" r:id="rId79" xr:uid="{22FF4B44-85C8-4FEA-84C6-CD60282E2194}"/>
+    <hyperlink ref="H45" r:id="rId80" xr:uid="{0E310210-E1DC-4F4A-92D6-F0ABDC0142BD}"/>
+    <hyperlink ref="H46" r:id="rId81" xr:uid="{FE5AEA26-E99D-45EF-B3F8-F823AF8149FB}"/>
+    <hyperlink ref="H47" r:id="rId82" xr:uid="{B0F0ED7F-B62C-4442-9610-04234546B2F7}"/>
+    <hyperlink ref="H48" r:id="rId83" xr:uid="{409FF414-B890-4FE2-A60E-D4FF3DF0D650}"/>
+    <hyperlink ref="H49" r:id="rId84" xr:uid="{ADA217C3-A76A-4FC8-BD12-8D2EB20D4621}"/>
+    <hyperlink ref="H50" r:id="rId85" xr:uid="{B4FC208A-BA8A-433E-91B1-0DE5579CBE73}"/>
+    <hyperlink ref="H51" r:id="rId86" xr:uid="{018FA14F-94FD-4A28-83C1-7E9A420F4224}"/>
+    <hyperlink ref="H52" r:id="rId87" xr:uid="{33E98605-5A80-460D-B7BC-959D621E91C3}"/>
+    <hyperlink ref="H53" r:id="rId88" xr:uid="{3D8EAEA8-35A8-49CF-AC39-E065E258EA59}"/>
+    <hyperlink ref="H54" r:id="rId89" xr:uid="{78ABA52C-0DD3-4FA0-8FC4-EBD6F6B83B85}"/>
+    <hyperlink ref="H55" r:id="rId90" xr:uid="{48AB4A2D-FB69-4885-A45A-51C843DD6423}"/>
+    <hyperlink ref="I48" r:id="rId91" xr:uid="{1C48030A-5FE7-4D37-888F-080297F158E0}"/>
+    <hyperlink ref="I50" r:id="rId92" xr:uid="{779E86D5-3180-4C77-93FD-E4F17E1636AB}"/>
+    <hyperlink ref="I52" r:id="rId93" xr:uid="{8D3DF093-DBC9-40E6-A795-ED0F55E48D86}"/>
+    <hyperlink ref="I53" r:id="rId94" xr:uid="{7D3D37C9-F914-4E3A-9F39-B0769FA723D0}"/>
+    <hyperlink ref="I54" r:id="rId95" xr:uid="{1BF1323C-FDF3-49AA-BBC4-9701C759CC7C}"/>
+    <hyperlink ref="I46" r:id="rId96" xr:uid="{A3AA1425-7F22-476F-9861-06AC3576504C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
